--- a/artfynd/A 6682-2023 artfynd.xlsx
+++ b/artfynd/A 6682-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6682-2023 artfynd.xlsx
+++ b/artfynd/A 6682-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>107154845</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481623.8090166943</v>
+        <v>481624</v>
       </c>
       <c r="R2" t="n">
-        <v>7064384.743846672</v>
+        <v>7064385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107154815</v>
+        <v>107154841</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åbodarna N Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481622.6215475723</v>
+        <v>481806</v>
       </c>
       <c r="R3" t="n">
-        <v>7064409.581523294</v>
+        <v>7064286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,24 +840,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107154814</v>
+        <v>107154795</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,11 +900,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481657.1100660371</v>
+        <v>481974</v>
       </c>
       <c r="R4" t="n">
-        <v>7064384.99368671</v>
+        <v>7064414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,19 +941,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1037,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107154806</v>
+        <v>107154796</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481865.2215112759</v>
+        <v>481862</v>
       </c>
       <c r="R5" t="n">
-        <v>7064595.733887075</v>
+        <v>7064665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1047,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1161,12 +1084,7 @@
         <v>107154797</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481783.740327523</v>
+        <v>481784</v>
       </c>
       <c r="R6" t="n">
-        <v>7064708.818915814</v>
+        <v>7064709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,19 +1157,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1283,15 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107154844</v>
+        <v>107154798</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,34 +1202,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Åbodarna N Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481712.3995770328</v>
+        <v>481835</v>
       </c>
       <c r="R7" t="n">
-        <v>7064348.756818086</v>
+        <v>7064760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,19 +1267,14 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,15 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107154843</v>
+        <v>107154799</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,34 +1312,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Åbodarna N Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481761.5865975989</v>
+        <v>481784</v>
       </c>
       <c r="R8" t="n">
-        <v>7064562.633718487</v>
+        <v>7064715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,19 +1377,14 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,15 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107154804</v>
+        <v>107154800</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,11 +1442,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1555,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481839.089652336</v>
+        <v>481815</v>
       </c>
       <c r="R9" t="n">
-        <v>7064606.525106725</v>
+        <v>7064677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,19 +1483,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1632,15 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107154810</v>
+        <v>107154801</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1548,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1676,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481676.1574604929</v>
+        <v>481786</v>
       </c>
       <c r="R10" t="n">
-        <v>7064377.345180032</v>
+        <v>7064638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,19 +1593,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1753,15 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107154796</v>
+        <v>107154802</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481862.5085237547</v>
+        <v>481712</v>
       </c>
       <c r="R11" t="n">
-        <v>7064664.47236147</v>
+        <v>7064649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,19 +1699,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1874,15 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107154799</v>
+        <v>107154803</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,11 +1764,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1922,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481784.661438288</v>
+        <v>481731</v>
       </c>
       <c r="R12" t="n">
-        <v>7064714.577312015</v>
+        <v>7064597</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1955,19 +1805,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1999,15 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107154798</v>
+        <v>107154804</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481835.0911046171</v>
+        <v>481839</v>
       </c>
       <c r="R13" t="n">
-        <v>7064760.396137583</v>
+        <v>7064606</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,19 +1915,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2124,15 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107154813</v>
+        <v>107154805</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481657.0868913487</v>
+        <v>481840</v>
       </c>
       <c r="R14" t="n">
-        <v>7064381.003144909</v>
+        <v>7064596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,19 +2021,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2245,15 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107154801</v>
+        <v>107154806</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,11 +2086,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2293,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481785.5508838184</v>
+        <v>481865</v>
       </c>
       <c r="R15" t="n">
-        <v>7064637.869656135</v>
+        <v>7064596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,19 +2127,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2370,15 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107154841</v>
+        <v>107154807</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,34 +2172,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åbodarna N Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481806.1667770832</v>
+        <v>481938</v>
       </c>
       <c r="R16" t="n">
-        <v>7064286.13687455</v>
+        <v>7064504</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,19 +2233,14 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,12 +2270,7 @@
         <v>107154808</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481733.598017194</v>
+        <v>481733</v>
       </c>
       <c r="R17" t="n">
-        <v>7064329.123915024</v>
+        <v>7064329</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,19 +2343,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2607,15 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107154811</v>
+        <v>107154809</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2643,11 +2408,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2655,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481673.9324119069</v>
+        <v>481731</v>
       </c>
       <c r="R18" t="n">
-        <v>7064376.471270498</v>
+        <v>7064398</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2688,19 +2449,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2732,15 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107154802</v>
+        <v>107154810</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481711.4738511324</v>
+        <v>481676</v>
       </c>
       <c r="R19" t="n">
-        <v>7064648.938676122</v>
+        <v>7064378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2809,19 +2555,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2853,15 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107154803</v>
+        <v>107154811</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,7 +2620,11 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2897,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481731.1512057786</v>
+        <v>481674</v>
       </c>
       <c r="R20" t="n">
-        <v>7064596.949942093</v>
+        <v>7064376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2930,19 +2665,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2974,15 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107154805</v>
+        <v>107154813</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481840.3577656662</v>
+        <v>481657</v>
       </c>
       <c r="R21" t="n">
-        <v>7064595.433374031</v>
+        <v>7064381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3051,19 +2771,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3095,15 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107154800</v>
+        <v>107154814</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3131,7 +2836,11 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3139,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481815.0783951546</v>
+        <v>481657</v>
       </c>
       <c r="R22" t="n">
-        <v>7064677.159410045</v>
+        <v>7064385</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3172,19 +2881,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3216,15 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107154809</v>
+        <v>107154815</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3252,7 +2946,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3260,10 +2958,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481730.8901874831</v>
+        <v>481623</v>
       </c>
       <c r="R23" t="n">
-        <v>7064398.311699734</v>
+        <v>7064410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3293,19 +2991,9 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3334,248 +3022,6 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>107154807</v>
-      </c>
-      <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Åbodarna N Föllinge, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>481938.3923623448</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7064503.53395994</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>107154795</v>
-      </c>
-      <c r="B25" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Åbodarna N Föllinge, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>481973.4007552495</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7064414.211095836</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6682-2023 artfynd.xlsx
+++ b/artfynd/A 6682-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154845</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154841</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154795</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154796</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154797</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154798</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154799</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154800</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154801</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,6 +1780,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154802</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1836,6 +1891,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154803</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154804</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154805</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2158,6 +2228,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154806</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2264,6 +2339,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154807</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154808</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2480,6 +2565,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154809</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2586,6 +2676,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154810</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2696,6 +2791,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154811</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154813</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2912,6 +3017,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154814</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3022,8 +3132,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107154815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>